--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D285457-058B-48B4-B455-4A2B488155E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C857EEC-40F6-413F-AFD4-602F6731350D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C857EEC-40F6-413F-AFD4-602F6731350D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E212C0F-56F3-426E-8380-2F96A377E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E212C0F-56F3-426E-8380-2F96A377E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3963963-5D88-4AF0-8CD5-1684CAE02709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3963963-5D88-4AF0-8CD5-1684CAE02709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34347CD-1251-48AB-8CCF-168F6D291F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34347CD-1251-48AB-8CCF-168F6D291F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA91FF4-6A86-4E20-AB65-6A5FADE8B9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA91FF4-6A86-4E20-AB65-6A5FADE8B9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A93988D-3818-4954-A6CF-1D307982F1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A93988D-3818-4954-A6CF-1D307982F1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA792A9-67D1-4A54-B971-995CC90A37BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA792A9-67D1-4A54-B971-995CC90A37BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCFE113-81B1-4911-A083-29526D506ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,76 +52,67 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
-    <t>KVARATSHIVILI</t>
-  </si>
-  <si>
-    <t>Abo</t>
-  </si>
-  <si>
-    <t>29/11/2006</t>
+    <t>KVARATSKHEILIA</t>
+  </si>
+  <si>
+    <t>Giorgi</t>
+  </si>
+  <si>
+    <t>13/03/2022</t>
   </si>
   <si>
     <t>Géorgie</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>MAKSHARPOV</t>
+  </si>
+  <si>
+    <t>Umar</t>
+  </si>
+  <si>
+    <t>21/01/1979</t>
+  </si>
+  <si>
+    <t>Tchétchénie</t>
+  </si>
+  <si>
+    <t>08/01/2023</t>
+  </si>
+  <si>
+    <t>MIAKHAIL</t>
+  </si>
+  <si>
+    <t>Karimullah</t>
+  </si>
+  <si>
+    <t>Afghanistan</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>NKAMBA</t>
+  </si>
+  <si>
+    <t>Albertina</t>
+  </si>
+  <si>
+    <t>10/05/1959</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
-    <t>KVARATSKHEILIA</t>
-  </si>
-  <si>
-    <t>Giorgi</t>
-  </si>
-  <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>MAKSHARPOV</t>
-  </si>
-  <si>
-    <t>Umar</t>
-  </si>
-  <si>
-    <t>21/01/1979</t>
-  </si>
-  <si>
-    <t>Tchétchénie</t>
-  </si>
-  <si>
-    <t>08/01/2023</t>
-  </si>
-  <si>
-    <t>MIAKHAIL</t>
-  </si>
-  <si>
-    <t>Karimullah</t>
-  </si>
-  <si>
-    <t>Afghanistan</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>NKAMBA</t>
-  </si>
-  <si>
-    <t>Albertina</t>
-  </si>
-  <si>
-    <t>10/05/1959</t>
-  </si>
-  <si>
-    <t>Angola</t>
   </si>
   <si>
     <t>25/02/2025</t>
@@ -789,13 +780,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
@@ -806,19 +797,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>24</v>
@@ -838,16 +829,16 @@
         <v>26</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>15</v>
@@ -858,22 +849,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -884,22 +875,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -910,22 +901,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -936,22 +927,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -974,10 +965,10 @@
         <v>12</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
@@ -988,22 +979,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1023,43 +1014,29 @@
         <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>12</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A16" s="6">

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCFE113-81B1-4911-A083-29526D506ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44ABB409-62EF-400D-B4BE-7AAF27FCB41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44ABB409-62EF-400D-B4BE-7AAF27FCB41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A30FCC-8FEE-4908-AF68-3D74A3618288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,6 +52,75 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
+    <t>AHMAD</t>
+  </si>
+  <si>
+    <t>Nafyad</t>
+  </si>
+  <si>
+    <t>11/06/1999</t>
+  </si>
+  <si>
+    <t>Éthiopie</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>AUGUSTO ANTONIO</t>
+  </si>
+  <si>
+    <t>Elizandre Maria</t>
+  </si>
+  <si>
+    <t>12/02/2006</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
+    <t>KARMA</t>
+  </si>
+  <si>
+    <t>Guyrme</t>
+  </si>
+  <si>
+    <t>08/02/1997</t>
+  </si>
+  <si>
+    <t>Tibet</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
+    <t>KVARATSHIVILI</t>
+  </si>
+  <si>
+    <t>Abo</t>
+  </si>
+  <si>
+    <t>29/11/2006</t>
+  </si>
+  <si>
+    <t>Géorgie</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
     <t>KVARATSKHEILIA</t>
   </si>
   <si>
@@ -61,18 +130,6 @@
     <t>13/03/2022</t>
   </si>
   <si>
-    <t>Géorgie</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>MAKSHARPOV</t>
   </si>
   <si>
@@ -94,6 +151,9 @@
     <t>Karimullah</t>
   </si>
   <si>
+    <t>31/12/1899</t>
+  </si>
+  <si>
     <t>Afghanistan</t>
   </si>
   <si>
@@ -109,12 +169,6 @@
     <t>10/05/1959</t>
   </si>
   <si>
-    <t>Angola</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>25/02/2025</t>
   </si>
   <si>
@@ -127,9 +181,6 @@
     <t>02/07/1991</t>
   </si>
   <si>
-    <t>Tibet</t>
-  </si>
-  <si>
     <t>07/10/2025</t>
   </si>
   <si>
@@ -143,9 +194,6 @@
   </si>
   <si>
     <t>Turquie</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
   </si>
   <si>
     <t>POHOSIAN</t>
@@ -803,16 +851,16 @@
         <v>22</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
@@ -823,22 +871,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>15</v>
@@ -849,22 +897,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -875,22 +923,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="E9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -901,22 +949,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -936,13 +984,13 @@
         <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -953,22 +1001,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
@@ -979,22 +1027,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1005,74 +1053,130 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>12</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="3"/>
+      <c r="B15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>13</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="3"/>
+      <c r="B16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>14</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="3"/>
+      <c r="B17" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>15</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="3"/>
+      <c r="B18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A19" s="6">

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A30FCC-8FEE-4908-AF68-3D74A3618288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F9F5CD-919C-46AA-B0F5-E8DAA55BA3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>Karimullah</t>
-  </si>
-  <si>
-    <t>31/12/1899</t>
   </si>
   <si>
     <t>Afghanistan</t>
@@ -955,16 +952,16 @@
         <v>41</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -975,13 +972,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>19</v>
@@ -990,7 +987,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1001,13 +998,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>24</v>
@@ -1016,7 +1013,7 @@
         <v>25</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
@@ -1027,16 +1024,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="E13" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>25</v>
@@ -1053,16 +1050,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="E14" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>25</v>
@@ -1079,13 +1076,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="13" t="s">
         <v>62</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>30</v>
@@ -1105,13 +1102,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>30</v>
@@ -1120,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1131,13 +1128,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>24</v>
@@ -1146,7 +1143,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -1157,22 +1154,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="E18" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F9F5CD-919C-46AA-B0F5-E8DAA55BA3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9003FF-B7D6-401B-A48F-5E2DCA5CC34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Nafyad</t>
   </si>
   <si>
-    <t>11/06/1999</t>
+    <t/>
   </si>
   <si>
     <t>Éthiopie</t>
@@ -67,84 +67,51 @@
     <t>F</t>
   </si>
   <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>AUGUSTO ANTONIO</t>
   </si>
   <si>
     <t>Elizandre Maria</t>
   </si>
   <si>
-    <t>12/02/2006</t>
-  </si>
-  <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
     <t>KARMA</t>
   </si>
   <si>
     <t>Guyrme</t>
   </si>
   <si>
-    <t>08/02/1997</t>
-  </si>
-  <si>
     <t>Tibet</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>08/10/2025</t>
-  </si>
-  <si>
     <t>KVARATSHIVILI</t>
   </si>
   <si>
     <t>Abo</t>
   </si>
   <si>
-    <t>29/11/2006</t>
-  </si>
-  <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
     <t>KVARATSKHEILIA</t>
   </si>
   <si>
     <t>Giorgi</t>
   </si>
   <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
     <t>MAKSHARPOV</t>
   </si>
   <si>
     <t>Umar</t>
   </si>
   <si>
-    <t>21/01/1979</t>
-  </si>
-  <si>
     <t>Tchétchénie</t>
   </si>
   <si>
-    <t>08/01/2023</t>
-  </si>
-  <si>
     <t>MIAKHAIL</t>
   </si>
   <si>
@@ -154,42 +121,24 @@
     <t>Afghanistan</t>
   </si>
   <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
     <t>NKAMBA</t>
   </si>
   <si>
     <t>Albertina</t>
   </si>
   <si>
-    <t>10/05/1959</t>
-  </si>
-  <si>
-    <t>25/02/2025</t>
-  </si>
-  <si>
     <t>NYINGPA</t>
   </si>
   <si>
     <t>Damchoe</t>
   </si>
   <si>
-    <t>02/07/1991</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
-  </si>
-  <si>
     <t>ONAL</t>
   </si>
   <si>
     <t>Ali Imran</t>
   </si>
   <si>
-    <t>18/08/2006</t>
-  </si>
-  <si>
     <t>Turquie</t>
   </si>
   <si>
@@ -199,9 +148,6 @@
     <t>Mykhailo</t>
   </si>
   <si>
-    <t>11/01/1953</t>
-  </si>
-  <si>
     <t>Ukraine</t>
   </si>
   <si>
@@ -211,43 +157,25 @@
     <t>Eldari</t>
   </si>
   <si>
-    <t>10/02/1985</t>
-  </si>
-  <si>
     <t>SHELIA</t>
   </si>
   <si>
     <t>Vakhtang</t>
   </si>
   <si>
-    <t>06/02/1963</t>
-  </si>
-  <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
     <t>TENZIN</t>
   </si>
   <si>
     <t>Nyima</t>
   </si>
   <si>
-    <t>10/06/1997</t>
-  </si>
-  <si>
     <t>TSANG</t>
   </si>
   <si>
     <t>Karma</t>
   </si>
   <si>
-    <t>15/05/1988</t>
-  </si>
-  <si>
     <t>Chine</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
   </si>
 </sst>
 </file>
@@ -805,10 +733,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -816,25 +744,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -842,25 +770,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -868,25 +796,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -894,25 +822,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -920,25 +848,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -946,25 +874,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -972,25 +900,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -998,25 +926,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1024,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1050,25 +978,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1076,25 +1004,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1102,25 +1030,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1128,25 +1056,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1154,25 +1082,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9003FF-B7D6-401B-A48F-5E2DCA5CC34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2347F1-A29F-4FF4-986F-C66A0F45F48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_1.xlsx
+++ b/Excel/liste_groupe_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2347F1-A29F-4FF4-986F-C66A0F45F48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D128BCFC-F418-47F5-8608-765B3B0904FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Nafyad</t>
   </si>
   <si>
-    <t/>
+    <t>11/06/1999</t>
   </si>
   <si>
     <t>Éthiopie</t>
@@ -67,51 +67,84 @@
     <t>F</t>
   </si>
   <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>AUGUSTO ANTONIO</t>
   </si>
   <si>
     <t>Elizandre Maria</t>
   </si>
   <si>
+    <t>12/02/2006</t>
+  </si>
+  <si>
     <t>Angola</t>
   </si>
   <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
     <t>KARMA</t>
   </si>
   <si>
     <t>Guyrme</t>
   </si>
   <si>
+    <t>08/02/1997</t>
+  </si>
+  <si>
     <t>Tibet</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
     <t>KVARATSHIVILI</t>
   </si>
   <si>
     <t>Abo</t>
   </si>
   <si>
+    <t>29/11/2006</t>
+  </si>
+  <si>
     <t>Géorgie</t>
   </si>
   <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
     <t>KVARATSKHEILIA</t>
   </si>
   <si>
     <t>Giorgi</t>
   </si>
   <si>
+    <t>13/03/2022</t>
+  </si>
+  <si>
     <t>MAKSHARPOV</t>
   </si>
   <si>
     <t>Umar</t>
   </si>
   <si>
+    <t>21/01/1979</t>
+  </si>
+  <si>
     <t>Tchétchénie</t>
   </si>
   <si>
+    <t>08/01/2023</t>
+  </si>
+  <si>
     <t>MIAKHAIL</t>
   </si>
   <si>
@@ -121,24 +154,42 @@
     <t>Afghanistan</t>
   </si>
   <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
     <t>NKAMBA</t>
   </si>
   <si>
     <t>Albertina</t>
   </si>
   <si>
+    <t>10/05/1959</t>
+  </si>
+  <si>
+    <t>25/02/2025</t>
+  </si>
+  <si>
     <t>NYINGPA</t>
   </si>
   <si>
     <t>Damchoe</t>
   </si>
   <si>
+    <t>02/07/1991</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
     <t>ONAL</t>
   </si>
   <si>
     <t>Ali Imran</t>
   </si>
   <si>
+    <t>18/08/2006</t>
+  </si>
+  <si>
     <t>Turquie</t>
   </si>
   <si>
@@ -148,6 +199,9 @@
     <t>Mykhailo</t>
   </si>
   <si>
+    <t>11/01/1953</t>
+  </si>
+  <si>
     <t>Ukraine</t>
   </si>
   <si>
@@ -157,25 +211,43 @@
     <t>Eldari</t>
   </si>
   <si>
+    <t>10/02/1985</t>
+  </si>
+  <si>
     <t>SHELIA</t>
   </si>
   <si>
     <t>Vakhtang</t>
   </si>
   <si>
+    <t>06/02/1963</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
     <t>TENZIN</t>
   </si>
   <si>
     <t>Nyima</t>
   </si>
   <si>
+    <t>10/06/1997</t>
+  </si>
+  <si>
     <t>TSANG</t>
   </si>
   <si>
     <t>Karma</t>
   </si>
   <si>
+    <t>15/05/1988</t>
+  </si>
+  <si>
     <t>Chine</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
   </si>
 </sst>
 </file>
@@ -733,10 +805,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -744,25 +816,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -770,25 +842,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -796,25 +868,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -822,25 +894,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G8" s="13" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -848,25 +920,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -874,25 +946,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -900,25 +972,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -926,25 +998,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -952,25 +1024,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -978,25 +1050,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1004,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1030,25 +1102,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1056,25 +1128,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1082,25 +1154,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
